--- a/templates/_masters/OPS-004-cleaning-cost-per-turnover-BLANK.xlsx
+++ b/templates/_masters/OPS-004-cleaning-cost-per-turnover-BLANK.xlsx
@@ -500,7 +500,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFE5C9"/>
+          <fgColor rgb="00FFF3BF"/>
         </patternFill>
       </fill>
     </dxf>
